--- a/multimodal_hw_00/Fabrication/PCBWAY_0626/BOM/Bill of Materials-multimodal_hw_00.xlsx
+++ b/multimodal_hw_00/Fabrication/PCBWAY_0626/BOM/Bill of Materials-multimodal_hw_00.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isili\OneDrive\Desktop\multimodal-hw-00\multimodal_hw_00\Fabrication\PCBWAY_050226\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isili\OneDrive\Desktop\multimodal-hw-00\multimodal_hw_00\Fabrication\PCBWAY_0626\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0EF5499-DCF4-4151-B7EF-C75483359E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587868BF-F420-4214-B130-5A6301745972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BB4CFBD-5B65-47F0-993B-39D641786693}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{1BB4CFBD-5B65-47F0-993B-39D641786693}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-multimodal_hw" sheetId="1" r:id="rId1"/>
@@ -1258,21 +1258,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A6BC1F-2432-47C3-8DDA-AE3BACA410CB}">
   <dimension ref="A1:L65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" customWidth="1"/>
-    <col min="7" max="7" width="27.5703125" customWidth="1"/>
-    <col min="8" max="8" width="23.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.3046875" customWidth="1"/>
+    <col min="2" max="4" width="16.53515625" customWidth="1"/>
+    <col min="5" max="5" width="11.3046875" customWidth="1"/>
+    <col min="6" max="6" width="16.53515625" customWidth="1"/>
+    <col min="7" max="7" width="27.53515625" customWidth="1"/>
+    <col min="8" max="8" width="23.84375" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="23.140625" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="23.15234375" customWidth="1"/>
+    <col min="11" max="11" width="20.53515625" customWidth="1"/>
+    <col min="12" max="12" width="19.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1458,7 +1458,7 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>0.94599999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>81.8</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -1596,7 +1596,7 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -1630,7 +1630,7 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>28.11</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1740,7 +1740,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>216.09</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>123.12</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -1888,7 +1888,7 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>12</v>
       </c>
@@ -1922,7 +1922,7 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>7.66</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
@@ -2024,7 +2024,7 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
         <v>12</v>
       </c>
@@ -2058,7 +2058,7 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
         <v>12</v>
       </c>
@@ -2092,7 +2092,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
@@ -2118,7 +2118,7 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
         <v>12</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
         <v>12</v>
       </c>
@@ -2256,7 +2256,7 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
@@ -2280,7 +2280,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
         <v>12</v>
       </c>
@@ -2304,7 +2304,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
@@ -2328,7 +2328,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -2390,7 +2390,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
         <v>12</v>
       </c>
@@ -2414,7 +2414,7 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>12</v>
       </c>
@@ -2514,7 +2514,7 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>12</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>12</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>12</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>12</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
         <v>12</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A43" s="2" t="s">
         <v>12</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A44" s="2" t="s">
         <v>12</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A46" s="2" t="s">
         <v>12</v>
       </c>
@@ -2852,7 +2852,7 @@
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A48" s="2" t="s">
         <v>12</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A50" s="2" t="s">
         <v>12</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A51" s="2" t="s">
         <v>12</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A52" s="2" t="s">
         <v>12</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A53" s="2" t="s">
         <v>12</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A54" s="2" t="s">
         <v>12</v>
       </c>
@@ -3146,7 +3146,7 @@
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A55" s="2" t="s">
         <v>12</v>
       </c>
@@ -3170,7 +3170,7 @@
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -3204,7 +3204,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -3228,7 +3228,7 @@
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A58" s="2" t="s">
         <v>12</v>
       </c>
@@ -3252,7 +3252,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A59" s="2" t="s">
         <v>12</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A60" s="2" t="s">
         <v>12</v>
       </c>
@@ -3314,7 +3314,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A61" s="2" t="s">
         <v>12</v>
       </c>
@@ -3338,7 +3338,7 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A62" s="2" t="s">
         <v>12</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A63" s="2" t="s">
         <v>12</v>
       </c>
@@ -3400,7 +3400,7 @@
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A64" s="2" t="s">
         <v>12</v>
       </c>
@@ -3428,7 +3428,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
